--- a/output/pdf_financials_xlsx/GOP.H.xlsx
+++ b/output/pdf_financials_xlsx/GOP.H.xlsx
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.14798</v>
+        <v>-0.14798</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-1.134597</v>
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.14798</v>
+        <v>-0.14798</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-1.134597</v>
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.14798</v>
+        <v>-0.14798</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-1.134597</v>
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-7.399</v>
+        <v>7.399</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.14798</v>
+        <v>-0.14798</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-1.134597</v>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.14798</v>
+        <v>-0.14798</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.969836</v>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -31375,7 +31375,7 @@
         <v>-1.134597</v>
       </c>
       <c r="H283" s="5" t="n">
-        <v>1.300838</v>
+        <v>-1.300838</v>
       </c>
       <c r="I283" t="inlineStr">
         <is>
@@ -31797,10 +31797,10 @@
         </is>
       </c>
       <c r="F288" s="5" t="n">
-        <v>0.14798</v>
+        <v>-0.14798</v>
       </c>
       <c r="G288" s="5" t="n">
-        <v>0.19144</v>
+        <v>-0.19144</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/GOP.H.xlsx
+++ b/output/pdf_financials_xlsx/GOP.H.xlsx
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000399</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000816</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.00278</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.225159</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1775,13 +1775,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.14798</v>
+        <v>-0.148796</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.134597</v>
+        <v>-1.137377</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.300838</v>
+        <v>-1.525997</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-1.892016</v>
@@ -1875,13 +1875,13 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.14798</v>
+        <v>-0.148796</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.969836</v>
+        <v>-0.972616</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.063345</v>
+        <v>-1.288504</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-1.616233</v>
@@ -1931,10 +1931,10 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-326.9381948611457</v>
+        <v>-327.8753514337147</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-23.75314660586524</v>
+        <v>-28.7827792618988</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>-37.73706892022866</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.291969</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>1.137154</v>
@@ -2129,28 +2129,28 @@
         <v>0.09023299999999999</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.045281</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.012285</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.002215</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.002273</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.002383</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.000136</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.005296</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.000659</v>
       </c>
     </row>
     <row r="35">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.291969</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>1.137154</v>
@@ -2231,28 +2231,28 @@
         <v>0.09023299999999999</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.045281</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.012285</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.002215</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.002273</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.002383</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.000136</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.005296</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.000659</v>
       </c>
     </row>
     <row r="37">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.325882</v>
+        <v>0.033913</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.007059</v>
@@ -2843,28 +2843,28 @@
         <v>0.052988</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.06098</v>
+        <v>0.015699</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.054613</v>
+        <v>1.042328</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.007636</v>
+        <v>0.005421</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.002273</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.002383</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.000136</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.005296</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.000659</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -12234,7 +12234,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -22740,7 +22740,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -28056,7 +28056,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -29022,7 +29022,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -29796,7 +29796,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -31442,7 +31442,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -32304,7 +32304,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E294" s="5" t="n">

--- a/output/pdf_financials_xlsx/GOP.H.xlsx
+++ b/output/pdf_financials_xlsx/GOP.H.xlsx
@@ -711,37 +711,37 @@
         <v>0.262712</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.88669</v>
+        <v>0.92419</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.745889</v>
+        <v>0.806639</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.5025539999999999</v>
+        <v>0.5640540000000001</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.35829</v>
+        <v>0.42604</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.29882</v>
+        <v>0.37532</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.102943</v>
+        <v>0.127943</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.084122</v>
+        <v>0.098122</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.06783</v>
+        <v>0.07983</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.055858</v>
+        <v>0.067858</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.072903</v>
+        <v>0.08490300000000001</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.068728</v>
+        <v>0.071728</v>
       </c>
     </row>
     <row r="8">
@@ -1418,16 +1418,16 @@
         <v>-1.892016</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-2.369162</v>
+        <v>-1.015386</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>-1.807175</v>
+        <v>-1.698896</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>-1.260833</v>
+        <v>-1.289047</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.920956</v>
+        <v>-0.203022</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>-0.11216</v>
@@ -2285,10 +2285,10 @@
         <v>1.320734</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0</v>
+        <v>2.109842</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0</v>
+        <v>2.109842</v>
       </c>
       <c r="K37" s="3" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>1.329042</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0</v>
+        <v>2.109842</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.006864</v>
+        <v>2.116706</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0.005599</v>
@@ -2846,10 +2846,10 @@
         <v>0.015699</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.042328</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.005421</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0</v>
@@ -20318,7 +20318,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -22896,7 +22900,11 @@
           <t>Director fees 7</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -25192,7 +25200,11 @@
           <t>Director fees 14</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
@@ -25606,7 +25618,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -26876,7 +26892,11 @@
           <t>Director fees 12</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -29282,7 +29302,11 @@
           <t>Director fees 13</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E259" t="inlineStr">
         <is>
           <t>-</t>
